--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:16:59+00:00</t>
+    <t>2026-06-05T12:18:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:18:27+00:00</t>
+    <t>2026-06-05T12:21:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-05T12:21:59+00:00</t>
+    <t>2026-06-05T13:35:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:27:17+00:00</t>
+    <t>2026-08-04T15:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T15:42:07+00:00</t>
+    <t>2026-08-07T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:47:42+00:00</t>
+    <t>2026-08-07T08:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:01:10+00:00</t>
+    <t>2026-08-07T08:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:58:25+00:00</t>
+    <t>2026-08-07T11:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T11:55:57+00:00</t>
+    <t>2026-08-10T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T12:42:53+00:00</t>
+    <t>2026-08-10T13:14:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:14:57+00:00</t>
+    <t>2026-08-10T13:29:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:29:34+00:00</t>
+    <t>2026-08-10T13:33:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:33:35+00:00</t>
+    <t>2026-08-10T13:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:39:12+00:00</t>
+    <t>2026-08-10T13:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:42:57+00:00</t>
+    <t>2026-08-10T13:45:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:45:29+00:00</t>
+    <t>2026-08-10T13:54:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -823,12 +823,11 @@
 </t>
   </si>
   <si>
-    <t>Reliabilility of the identity | Fiabilité de l'identité</t>
-  </si>
-  <si>
-    <t>Précision sur le degré de fiabilité de l'identité du patient (si provisoire, validé... avec la justification : quelle type de pièce d'identité ?) accompagné de la méthode de collection.
--Reliabilility of the patient's identity</t>
+    <t>FR Core Patient Identity Reliability Extension</t>
+  </si>
+  <si>
+    <t>Extension composite précisant le degré de confiance de l'identité du patient au sens du Référentiel National d'Identitovigilance (RNIV) : statut de confiance (provisoire, récupérée, validée, qualifiée), canal d'obtention des traits d'identité ou de l'INS, pièce justificative contrôlée, dates associées et annotations complémentaires.
+Composite extension specifying the confidence level of a patient's identity per the French National Identity Vigilance Framework (RNIV): trust status (provisional, recovered, validated, qualified), channel used to collect the identity traits or the INS, validation evidence, related dates and additional annotations.</t>
   </si>
   <si>
     <t>Patient.extension:deathPlace</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T13:54:17+00:00</t>
+    <t>2026-08-10T14:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:12:55+00:00</t>
+    <t>2026-08-10T14:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -826,8 +826,8 @@
     <t>FR Core Patient Identity Reliability Extension</t>
   </si>
   <si>
-    <t>Extension composite précisant le degré de confiance de l'identité du patient au sens du Référentiel National d'Identitovigilance (RNIV) : statut de confiance (provisoire, récupérée, validée, qualifiée), canal d'obtention des traits d'identité ou de l'INS, pièce justificative contrôlée, dates associées et annotations complémentaires.
-Composite extension specifying the confidence level of a patient's identity per the French National Identity Vigilance Framework (RNIV): trust status (provisional, recovered, validated, qualified), channel used to collect the identity traits or the INS, validation evidence, related dates and additional annotations.</t>
+    <t>Extension composite précisant le degré de confiance de l'identité du patient au sens du Référentiel National d'Identitovigilance (RNIV) : statut de confiance (provisoire, récupérée, validée, qualifiée), canal d'obtention des traits d'identité ou du matricule INS, pièce justificative contrôlée, dates associées et annotations complémentaires.
+Composite extension specifying the confidence level of a patient's identity per the French National Identity Vigilance Framework (RNIV): trust status (provisional, recovered, validated, qualified), channel used to collect the identity traits or the INS identifier, validation evidence, related dates and additional annotations.</t>
   </si>
   <si>
     <t>Patient.extension:deathPlace</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:29:18+00:00</t>
+    <t>2026-08-10T16:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:19:09+00:00</t>
+    <t>2026-08-10T16:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:22:30+00:00</t>
+    <t>2026-08-10T16:46:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T16:46:59+00:00</t>
+    <t>2026-08-11T07:24:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T07:24:13+00:00</t>
+    <t>2026-08-11T10:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:04:20+00:00</t>
+    <t>2026-08-11T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T11:39:02+00:00</t>
+    <t>2026-08-12T13:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T13:53:29+00:00</t>
+    <t>2026-08-12T14:08:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
